--- a/EKG_Kalite_Yönetim_Sistemi/06_Garanti Sorunları Yönetimi/01_WIM1 - Koordinatör, Portal ve İade Parça/EKG-KLT-LST-07_garanti_portali_gunluk_inceleme_ve_pareto_kaydi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/06_Garanti Sorunları Yönetimi/01_WIM1 - Koordinatör, Portal ve İade Parça/EKG-KLT-LST-07_garanti_portali_gunluk_inceleme_ve_pareto_kaydi.xlsx
@@ -952,7 +952,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-LST-07&amp;C&amp;"Arial,Regular"&amp;11Garanti Portalı Günlük İnceleme ve Pareto Kaydı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Garanti kayıt kategorileri cam ürünlerine uyarlandı; boş veri ve Pareto/Paynter sayım kuralları düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1187,7 +1188,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-LST-07&amp;C&amp;"Arial,Regular"&amp;11Garanti Portalı Günlük İnceleme ve Pareto Kaydı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 21.09.2026
+Revizyon nedeni: Garanti kayıt kategorileri cam ürünlerine uyarlandı; boş veri ve Pareto/Paynter sayım kuralları düzeltildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>